--- a/outputs/all_tables.xlsx
+++ b/outputs/all_tables.xlsx
@@ -20746,28 +20746,28 @@
         <v>0.722</v>
       </c>
       <c r="M2" t="n">
-        <v>0.526</v>
+        <v>0.527</v>
       </c>
       <c r="N2" t="n">
-        <v>0.863</v>
+        <v>0.865</v>
       </c>
       <c r="O2" t="n">
         <v>0.899</v>
       </c>
       <c r="P2" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.965</v>
+        <v>0.966</v>
       </c>
       <c r="R2" t="n">
         <v>14.38</v>
       </c>
       <c r="S2" t="n">
-        <v>10.955</v>
+        <v>10.971</v>
       </c>
       <c r="T2" t="n">
-        <v>18.362</v>
+        <v>18.355</v>
       </c>
     </row>
     <row r="3">
@@ -20783,16 +20783,16 @@
         <v>0.364</v>
       </c>
       <c r="D3" t="n">
-        <v>0.165</v>
+        <v>0.163</v>
       </c>
       <c r="E3" t="n">
-        <v>0.611</v>
+        <v>0.617</v>
       </c>
       <c r="F3" t="n">
         <v>0.98</v>
       </c>
       <c r="G3" t="n">
-        <v>0.576</v>
+        <v>0.572</v>
       </c>
       <c r="H3" t="n">
         <v>0.987</v>
@@ -20801,37 +20801,37 @@
         <v>4.358</v>
       </c>
       <c r="J3" t="n">
-        <v>2.283</v>
+        <v>2.291</v>
       </c>
       <c r="K3" t="n">
-        <v>8.157</v>
+        <v>8.201000000000001</v>
       </c>
       <c r="L3" t="n">
         <v>0.502</v>
       </c>
       <c r="M3" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="N3" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="O3" t="n">
         <v>0.909</v>
       </c>
       <c r="P3" t="n">
-        <v>0.613</v>
+        <v>0.616</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.952</v>
+        <v>0.951</v>
       </c>
       <c r="R3" t="n">
         <v>6.433</v>
       </c>
       <c r="S3" t="n">
-        <v>3.96</v>
+        <v>3.951</v>
       </c>
       <c r="T3" t="n">
-        <v>10.062</v>
+        <v>10.047</v>
       </c>
     </row>
     <row r="4">
@@ -20847,34 +20847,34 @@
         <v>0.574</v>
       </c>
       <c r="D4" t="n">
-        <v>0.167</v>
+        <v>0.164</v>
       </c>
       <c r="E4" t="n">
-        <v>0.917</v>
+        <v>0.918</v>
       </c>
       <c r="F4" t="n">
         <v>0.312</v>
       </c>
       <c r="G4" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>3.806</v>
       </c>
       <c r="J4" t="n">
-        <v>2.029</v>
+        <v>2.037</v>
       </c>
       <c r="K4" t="n">
-        <v>7.441</v>
+        <v>7.354</v>
       </c>
       <c r="L4" t="n">
         <v>0.574</v>
       </c>
       <c r="M4" t="n">
-        <v>0.162</v>
+        <v>0.165</v>
       </c>
       <c r="N4" t="n">
         <v>0.919</v>
@@ -20883,19 +20883,19 @@
         <v>0.331</v>
       </c>
       <c r="P4" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.714</v>
+        <v>0.71</v>
       </c>
       <c r="R4" t="n">
         <v>3.618</v>
       </c>
       <c r="S4" t="n">
-        <v>1.871</v>
+        <v>1.905</v>
       </c>
       <c r="T4" t="n">
-        <v>7.237</v>
+        <v>7.166</v>
       </c>
     </row>
     <row r="5">
@@ -20911,7 +20911,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.573</v>
+        <v>0.576</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -20920,25 +20920,25 @@
         <v>0.948</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.971</v>
+        <v>0.97</v>
       </c>
       <c r="I5" t="n">
         <v>3.126</v>
       </c>
       <c r="J5" t="n">
-        <v>2.966</v>
+        <v>1.743</v>
       </c>
       <c r="K5" t="n">
-        <v>5.057</v>
+        <v>4.681</v>
       </c>
       <c r="L5" t="n">
         <v>0.661</v>
       </c>
       <c r="M5" t="n">
-        <v>0.374</v>
+        <v>0.372</v>
       </c>
       <c r="N5" t="n">
         <v>0.821</v>
@@ -20947,7 +20947,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -20956,10 +20956,10 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.784</v>
+        <v>1.087</v>
       </c>
       <c r="T5" t="n">
-        <v>4.074</v>
+        <v>3.964</v>
       </c>
     </row>
     <row r="6">
@@ -20975,7 +20975,7 @@
         <v>0.798</v>
       </c>
       <c r="D6" t="n">
-        <v>0.585</v>
+        <v>0.584</v>
       </c>
       <c r="E6" t="n">
         <v>0.908</v>
@@ -20984,25 +20984,25 @@
         <v>0.913</v>
       </c>
       <c r="G6" t="n">
-        <v>0.74</v>
+        <v>0.735</v>
       </c>
       <c r="H6" t="n">
-        <v>0.95</v>
+        <v>0.949</v>
       </c>
       <c r="I6" t="n">
         <v>11.87</v>
       </c>
       <c r="J6" t="n">
-        <v>8.819000000000001</v>
+        <v>8.865</v>
       </c>
       <c r="K6" t="n">
-        <v>14.562</v>
+        <v>14.585</v>
       </c>
       <c r="L6" t="n">
         <v>0.787</v>
       </c>
       <c r="M6" t="n">
-        <v>0.575</v>
+        <v>0.576</v>
       </c>
       <c r="N6" t="n">
         <v>0.899</v>
@@ -21011,19 +21011,19 @@
         <v>0.924</v>
       </c>
       <c r="P6" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.957</v>
+        <v>0.956</v>
       </c>
       <c r="R6" t="n">
         <v>11.622</v>
       </c>
       <c r="S6" t="n">
-        <v>8.635999999999999</v>
+        <v>8.614000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>14.315</v>
+        <v>14.319</v>
       </c>
     </row>
     <row r="7">
@@ -21039,55 +21039,55 @@
         <v>0.421</v>
       </c>
       <c r="D7" t="n">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="E7" t="n">
-        <v>0.657</v>
+        <v>0.66</v>
       </c>
       <c r="F7" t="n">
         <v>0.613</v>
       </c>
       <c r="G7" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="H7" t="n">
-        <v>0.761</v>
+        <v>0.756</v>
       </c>
       <c r="I7" t="n">
         <v>5.097</v>
       </c>
       <c r="J7" t="n">
-        <v>4.202</v>
+        <v>4.188</v>
       </c>
       <c r="K7" t="n">
-        <v>7.656</v>
+        <v>7.568</v>
       </c>
       <c r="L7" t="n">
         <v>0.343</v>
       </c>
       <c r="M7" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="N7" t="n">
-        <v>0.586</v>
+        <v>0.584</v>
       </c>
       <c r="O7" t="n">
         <v>0.977</v>
       </c>
       <c r="P7" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.985</v>
+        <v>0.984</v>
       </c>
       <c r="R7" t="n">
         <v>2.156</v>
       </c>
       <c r="S7" t="n">
-        <v>1.618</v>
+        <v>1.615</v>
       </c>
       <c r="T7" t="n">
-        <v>4.647</v>
+        <v>4.588</v>
       </c>
     </row>
     <row r="8">
@@ -21103,7 +21103,7 @@
         <v>0.8169999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.572</v>
       </c>
       <c r="E8" t="n">
         <v>0.896</v>
@@ -21112,34 +21112,34 @@
         <v>0.67</v>
       </c>
       <c r="G8" t="n">
-        <v>0.414</v>
+        <v>0.417</v>
       </c>
       <c r="H8" t="n">
-        <v>0.847</v>
+        <v>0.848</v>
       </c>
       <c r="I8" t="n">
         <v>8.715</v>
       </c>
       <c r="J8" t="n">
-        <v>6.107</v>
+        <v>6.11</v>
       </c>
       <c r="K8" t="n">
-        <v>11.756</v>
+        <v>11.783</v>
       </c>
       <c r="L8" t="n">
         <v>0.551</v>
       </c>
       <c r="M8" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
       <c r="N8" t="n">
-        <v>0.771</v>
+        <v>0.767</v>
       </c>
       <c r="O8" t="n">
         <v>0.645</v>
       </c>
       <c r="P8" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="Q8" t="n">
         <v>0.875</v>
@@ -21148,10 +21148,10 @@
         <v>5.345</v>
       </c>
       <c r="S8" t="n">
-        <v>3.462</v>
+        <v>3.491</v>
       </c>
       <c r="T8" t="n">
-        <v>9.369</v>
+        <v>9.396000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -21167,7 +21167,7 @@
         <v>0.972</v>
       </c>
       <c r="D9" t="n">
-        <v>0.736</v>
+        <v>0.739</v>
       </c>
       <c r="E9" t="n">
         <v>0.985</v>
@@ -21176,28 +21176,28 @@
         <v>0.725</v>
       </c>
       <c r="G9" t="n">
-        <v>0.497</v>
+        <v>0.496</v>
       </c>
       <c r="H9" t="n">
-        <v>0.864</v>
+        <v>0.862</v>
       </c>
       <c r="I9" t="n">
         <v>13.494</v>
       </c>
       <c r="J9" t="n">
-        <v>10.613</v>
+        <v>10.665</v>
       </c>
       <c r="K9" t="n">
-        <v>16.449</v>
+        <v>16.417</v>
       </c>
       <c r="L9" t="n">
         <v>0.832</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0.764</v>
@@ -21206,16 +21206,16 @@
         <v>0.521</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.881</v>
+        <v>0.882</v>
       </c>
       <c r="R9" t="n">
         <v>11.108</v>
       </c>
       <c r="S9" t="n">
-        <v>8.172000000000001</v>
+        <v>8.182</v>
       </c>
       <c r="T9" t="n">
-        <v>14.042</v>
+        <v>14.192</v>
       </c>
     </row>
     <row r="10">
@@ -21231,10 +21231,10 @@
         <v>0.928</v>
       </c>
       <c r="D10" t="n">
-        <v>0.744</v>
+        <v>0.741</v>
       </c>
       <c r="E10" t="n">
-        <v>0.959</v>
+        <v>0.958</v>
       </c>
       <c r="F10" t="n">
         <v>0.793</v>
@@ -21243,16 +21243,16 @@
         <v>0.577</v>
       </c>
       <c r="H10" t="n">
-        <v>0.909</v>
+        <v>0.908</v>
       </c>
       <c r="I10" t="n">
         <v>12.49</v>
       </c>
       <c r="J10" t="n">
-        <v>10.127</v>
+        <v>10.162</v>
       </c>
       <c r="K10" t="n">
-        <v>15.609</v>
+        <v>15.58</v>
       </c>
       <c r="L10" t="n">
         <v>0.9360000000000001</v>
@@ -21261,16 +21261,16 @@
         <v>0.752</v>
       </c>
       <c r="N10" t="n">
-        <v>0.964</v>
+        <v>0.965</v>
       </c>
       <c r="O10" t="n">
         <v>0.656</v>
       </c>
       <c r="P10" t="n">
-        <v>0.462</v>
+        <v>0.464</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R10" t="n">
         <v>14.864</v>
@@ -21279,7 +21279,7 @@
         <v>11.894</v>
       </c>
       <c r="T10" t="n">
-        <v>18.777</v>
+        <v>18.717</v>
       </c>
     </row>
     <row r="11">
@@ -21295,10 +21295,10 @@
         <v>0.581</v>
       </c>
       <c r="D11" t="n">
-        <v>0.382</v>
+        <v>0.386</v>
       </c>
       <c r="E11" t="n">
-        <v>0.746</v>
+        <v>0.75</v>
       </c>
       <c r="F11" t="n">
         <v>0.5600000000000001</v>
@@ -21307,25 +21307,25 @@
         <v>0.375</v>
       </c>
       <c r="H11" t="n">
-        <v>0.711</v>
+        <v>0.713</v>
       </c>
       <c r="I11" t="n">
         <v>12.446</v>
       </c>
       <c r="J11" t="n">
-        <v>9.58</v>
+        <v>9.603</v>
       </c>
       <c r="K11" t="n">
-        <v>16.872</v>
+        <v>16.816</v>
       </c>
       <c r="L11" t="n">
         <v>0.848</v>
       </c>
       <c r="M11" t="n">
-        <v>0.665</v>
+        <v>0.666</v>
       </c>
       <c r="N11" t="n">
-        <v>0.923</v>
+        <v>0.922</v>
       </c>
       <c r="O11" t="n">
         <v>0.447</v>
@@ -21334,16 +21334,16 @@
         <v>0.315</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.581</v>
+        <v>0.58</v>
       </c>
       <c r="R11" t="n">
         <v>23.283</v>
       </c>
       <c r="S11" t="n">
-        <v>19.06</v>
+        <v>19.049</v>
       </c>
       <c r="T11" t="n">
-        <v>28.505</v>
+        <v>28.679</v>
       </c>
     </row>
   </sheetData>
@@ -21482,10 +21482,10 @@
         <v>0.58</v>
       </c>
       <c r="I3" t="n">
-        <v>0.58</v>
+        <v>0.19</v>
       </c>
       <c r="J3" t="n">
-        <v>4.68</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="4">
@@ -21511,19 +21511,19 @@
         <v>22.71</v>
       </c>
       <c r="F4" t="n">
-        <v>17.1</v>
+        <v>17.17</v>
       </c>
       <c r="G4" t="n">
-        <v>28.1</v>
+        <v>28.05</v>
       </c>
       <c r="H4" t="n">
         <v>23.86</v>
       </c>
       <c r="I4" t="n">
-        <v>18.16</v>
+        <v>18.15</v>
       </c>
       <c r="J4" t="n">
-        <v>31.06</v>
+        <v>31.03</v>
       </c>
     </row>
     <row r="5">
@@ -21549,19 +21549,19 @@
         <v>1.76</v>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="G5" t="n">
-        <v>5.13</v>
+        <v>5.09</v>
       </c>
       <c r="H5" t="n">
         <v>0.53</v>
       </c>
       <c r="I5" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="J5" t="n">
-        <v>4.67</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="6">
@@ -21587,7 +21587,7 @@
         <v>6.23</v>
       </c>
       <c r="F6" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="G6" t="n">
         <v>11.22</v>
@@ -21596,10 +21596,10 @@
         <v>6.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="J6" t="n">
-        <v>12.41</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="7">
@@ -21625,19 +21625,19 @@
         <v>1.52</v>
       </c>
       <c r="F7" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="H7" t="n">
         <v>1.08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="J7" t="n">
-        <v>5.42</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="8">
@@ -21663,19 +21663,19 @@
         <v>8.99</v>
       </c>
       <c r="F8" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="G8" t="n">
-        <v>13.74</v>
+        <v>13.66</v>
       </c>
       <c r="H8" t="n">
         <v>9.43</v>
       </c>
       <c r="I8" t="n">
-        <v>5.97</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>15.32</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="9">
@@ -21701,19 +21701,19 @@
         <v>2.56</v>
       </c>
       <c r="F9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="H9" t="n">
         <v>1.93</v>
       </c>
       <c r="I9" t="n">
-        <v>1.83</v>
+        <v>0.48</v>
       </c>
       <c r="J9" t="n">
-        <v>6.18</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="10">
@@ -21742,16 +21742,16 @@
         <v>2.55</v>
       </c>
       <c r="G10" t="n">
-        <v>8.42</v>
+        <v>8.48</v>
       </c>
       <c r="H10" t="n">
         <v>6.88</v>
       </c>
       <c r="I10" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="J10" t="n">
-        <v>13.68</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="11">
@@ -21777,19 +21777,19 @@
         <v>2.33</v>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G11" t="n">
-        <v>5.94</v>
+        <v>5.93</v>
       </c>
       <c r="H11" t="n">
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>4.39</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="12">
@@ -21815,10 +21815,10 @@
         <v>4.64</v>
       </c>
       <c r="F12" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="G12" t="n">
-        <v>8.31</v>
+        <v>8.32</v>
       </c>
       <c r="H12" t="n">
         <v>6.58</v>
@@ -21827,7 +21827,7 @@
         <v>3.35</v>
       </c>
       <c r="J12" t="n">
-        <v>13.49</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="13">
@@ -21853,19 +21853,19 @@
         <v>2.07</v>
       </c>
       <c r="F13" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>5.66</v>
+        <v>5.64</v>
       </c>
       <c r="H13" t="n">
         <v>0.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>4.27</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="14">
@@ -21891,19 +21891,19 @@
         <v>5.05</v>
       </c>
       <c r="F14" t="n">
-        <v>4.78</v>
+        <v>2.77</v>
       </c>
       <c r="G14" t="n">
-        <v>6.99</v>
+        <v>6.25</v>
       </c>
       <c r="H14" t="n">
         <v>5.14</v>
       </c>
       <c r="I14" t="n">
-        <v>4.87</v>
+        <v>2.91</v>
       </c>
       <c r="J14" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="15">
@@ -21929,19 +21929,19 @@
         <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J15" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="16">
@@ -21967,19 +21967,19 @@
         <v>3.28</v>
       </c>
       <c r="F16" t="n">
-        <v>2.87</v>
+        <v>1.74</v>
       </c>
       <c r="G16" t="n">
-        <v>5.32</v>
+        <v>5.33</v>
       </c>
       <c r="H16" t="n">
         <v>3.28</v>
       </c>
       <c r="I16" t="n">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="J16" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="17">
@@ -22005,19 +22005,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G17" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J17" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="18">
@@ -22043,19 +22043,19 @@
         <v>10.99</v>
       </c>
       <c r="F18" t="n">
-        <v>8.33</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>13.59</v>
+        <v>13.56</v>
       </c>
       <c r="H18" t="n">
         <v>4.27</v>
       </c>
       <c r="I18" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="J18" t="n">
-        <v>11.55</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="19">
@@ -22081,19 +22081,19 @@
         <v>13.21</v>
       </c>
       <c r="F19" t="n">
-        <v>9.65</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>16.17</v>
+        <v>16.15</v>
       </c>
       <c r="H19" t="n">
         <v>15.79</v>
       </c>
       <c r="I19" t="n">
-        <v>12.76</v>
+        <v>12.68</v>
       </c>
       <c r="J19" t="n">
-        <v>19.23</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="20">
@@ -22119,19 +22119,19 @@
         <v>10.76</v>
       </c>
       <c r="F20" t="n">
-        <v>8.130000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="G20" t="n">
-        <v>13.37</v>
+        <v>13.36</v>
       </c>
       <c r="H20" t="n">
         <v>4.17</v>
       </c>
       <c r="I20" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="J20" t="n">
-        <v>11.43</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="21">
@@ -22157,19 +22157,19 @@
         <v>12.93</v>
       </c>
       <c r="F21" t="n">
-        <v>9.380000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="G21" t="n">
-        <v>15.83</v>
+        <v>15.89</v>
       </c>
       <c r="H21" t="n">
         <v>15.38</v>
       </c>
       <c r="I21" t="n">
-        <v>12.28</v>
+        <v>12.31</v>
       </c>
       <c r="J21" t="n">
-        <v>18.88</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="22">
@@ -22195,19 +22195,19 @@
         <v>3.64</v>
       </c>
       <c r="F22" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1</v>
+        <v>6.08</v>
       </c>
       <c r="H22" t="n">
         <v>3.91</v>
       </c>
       <c r="I22" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="J22" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -22233,19 +22233,19 @@
         <v>7.3</v>
       </c>
       <c r="F23" t="n">
-        <v>5.74</v>
+        <v>5.78</v>
       </c>
       <c r="G23" t="n">
-        <v>10.35</v>
+        <v>10.33</v>
       </c>
       <c r="H23" t="n">
         <v>6.98</v>
       </c>
       <c r="I23" t="n">
-        <v>5.47</v>
+        <v>5.44</v>
       </c>
       <c r="J23" t="n">
-        <v>11.85</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="24">
@@ -22271,19 +22271,19 @@
         <v>0.65</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H24" t="n">
         <v>0.29</v>
       </c>
       <c r="I24" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="J24" t="n">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="25">
@@ -22309,19 +22309,19 @@
         <v>4.44</v>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="G25" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="H25" t="n">
         <v>5.06</v>
       </c>
       <c r="I25" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="J25" t="n">
-        <v>10.04</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -22347,7 +22347,7 @@
         <v>10.89</v>
       </c>
       <c r="F26" t="n">
-        <v>7.46</v>
+        <v>7.42</v>
       </c>
       <c r="G26" t="n">
         <v>13.73</v>
@@ -22356,10 +22356,10 @@
         <v>12.91</v>
       </c>
       <c r="I26" t="n">
-        <v>8.1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>18.7</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="27">
@@ -22385,19 +22385,19 @@
         <v>5.41</v>
       </c>
       <c r="F27" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="G27" t="n">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="H27" t="n">
         <v>3.03</v>
       </c>
       <c r="I27" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
-        <v>6.91</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="28">
@@ -22423,19 +22423,19 @@
         <v>6.18</v>
       </c>
       <c r="F28" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="G28" t="n">
-        <v>10.75</v>
+        <v>10.74</v>
       </c>
       <c r="H28" t="n">
         <v>8.68</v>
       </c>
       <c r="I28" t="n">
-        <v>4.79</v>
+        <v>4.73</v>
       </c>
       <c r="J28" t="n">
-        <v>15.69</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="29">
@@ -22470,10 +22470,10 @@
         <v>2.17</v>
       </c>
       <c r="I29" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>6.53</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="30">
@@ -22499,19 +22499,19 @@
         <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>15.83</v>
+        <v>15.71</v>
       </c>
       <c r="G30" t="n">
-        <v>22.6</v>
+        <v>22.51</v>
       </c>
       <c r="H30" t="n">
         <v>22.44</v>
       </c>
       <c r="I30" t="n">
-        <v>17.53</v>
+        <v>17.59</v>
       </c>
       <c r="J30" t="n">
-        <v>28.02</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="31">
@@ -22537,19 +22537,19 @@
         <v>3.64</v>
       </c>
       <c r="F31" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="G31" t="n">
-        <v>7.35</v>
+        <v>7.32</v>
       </c>
       <c r="H31" t="n">
         <v>0.71</v>
       </c>
       <c r="I31" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
-        <v>4.84</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="32">
@@ -22575,19 +22575,19 @@
         <v>16.68</v>
       </c>
       <c r="F32" t="n">
-        <v>12.03</v>
+        <v>12.04</v>
       </c>
       <c r="G32" t="n">
-        <v>19.95</v>
+        <v>19.87</v>
       </c>
       <c r="H32" t="n">
         <v>18.09</v>
       </c>
       <c r="I32" t="n">
-        <v>13.24</v>
+        <v>13.28</v>
       </c>
       <c r="J32" t="n">
-        <v>23.65</v>
+        <v>23.79</v>
       </c>
     </row>
     <row r="33">
@@ -22616,16 +22616,16 @@
         <v>1.71</v>
       </c>
       <c r="G33" t="n">
-        <v>5.81</v>
+        <v>5.8</v>
       </c>
       <c r="H33" t="n">
         <v>0.92</v>
       </c>
       <c r="I33" t="n">
-        <v>0.87</v>
+        <v>0.43</v>
       </c>
       <c r="J33" t="n">
-        <v>4.96</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="34">
@@ -22651,19 +22651,19 @@
         <v>18.91</v>
       </c>
       <c r="F34" t="n">
-        <v>15.4</v>
+        <v>15.44</v>
       </c>
       <c r="G34" t="n">
-        <v>21.69</v>
+        <v>21.67</v>
       </c>
       <c r="H34" t="n">
         <v>21.12</v>
       </c>
       <c r="I34" t="n">
-        <v>16.93</v>
+        <v>16.91</v>
       </c>
       <c r="J34" t="n">
-        <v>27.15</v>
+        <v>27.18</v>
       </c>
     </row>
     <row r="35">
@@ -22689,19 +22689,19 @@
         <v>2.76</v>
       </c>
       <c r="F35" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="G35" t="n">
-        <v>6.48</v>
+        <v>6.6</v>
       </c>
       <c r="H35" t="n">
         <v>0.31</v>
       </c>
       <c r="I35" t="n">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="J35" t="n">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="36">
@@ -22727,19 +22727,19 @@
         <v>21.16</v>
       </c>
       <c r="F36" t="n">
-        <v>17.28</v>
+        <v>17.33</v>
       </c>
       <c r="G36" t="n">
-        <v>24.65</v>
+        <v>24.61</v>
       </c>
       <c r="H36" t="n">
         <v>25.68</v>
       </c>
       <c r="I36" t="n">
-        <v>20.07</v>
+        <v>19.98</v>
       </c>
       <c r="J36" t="n">
-        <v>33</v>
+        <v>32.92</v>
       </c>
     </row>
     <row r="37">
@@ -22765,19 +22765,19 @@
         <v>5.33</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="H37" t="n">
         <v>0.32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="J37" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="38">
@@ -22803,10 +22803,10 @@
         <v>12.22</v>
       </c>
       <c r="F38" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="G38" t="n">
-        <v>16.52</v>
+        <v>16.57</v>
       </c>
       <c r="H38" t="n">
         <v>9.210000000000001</v>
@@ -22815,7 +22815,7 @@
         <v>6.24</v>
       </c>
       <c r="J38" t="n">
-        <v>15.54</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="39">
@@ -22844,16 +22844,16 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>17.35</v>
+        <v>17.29</v>
       </c>
       <c r="H39" t="n">
         <v>16.66</v>
       </c>
       <c r="I39" t="n">
-        <v>12.18</v>
+        <v>12.23</v>
       </c>
       <c r="J39" t="n">
-        <v>23.78</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="40">
@@ -22879,19 +22879,19 @@
         <v>23.16</v>
       </c>
       <c r="F40" t="n">
-        <v>18.97</v>
+        <v>19.04</v>
       </c>
       <c r="G40" t="n">
-        <v>28.5</v>
+        <v>28.51</v>
       </c>
       <c r="H40" t="n">
         <v>22.01</v>
       </c>
       <c r="I40" t="n">
-        <v>17.19</v>
+        <v>17.25</v>
       </c>
       <c r="J40" t="n">
-        <v>29.35</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="41">
@@ -22917,19 +22917,19 @@
         <v>23.47</v>
       </c>
       <c r="F41" t="n">
-        <v>19.17</v>
+        <v>19.14</v>
       </c>
       <c r="G41" t="n">
-        <v>28.84</v>
+        <v>28.75</v>
       </c>
       <c r="H41" t="n">
         <v>24.67</v>
       </c>
       <c r="I41" t="n">
-        <v>18.35</v>
+        <v>18.29</v>
       </c>
       <c r="J41" t="n">
-        <v>32.99</v>
+        <v>33.06</v>
       </c>
     </row>
   </sheetData>
@@ -23057,7 +23057,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -23089,10 +23089,10 @@
         <v>3.85</v>
       </c>
       <c r="G4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="H4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>66</v>
@@ -23127,7 +23127,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23159,10 +23159,10 @@
         <v>0.67</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23229,10 +23229,10 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="n">
-        <v>8.07</v>
+        <v>8.08</v>
       </c>
       <c r="I8" t="n">
         <v>22</v>
@@ -23267,7 +23267,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -23299,7 +23299,7 @@
         <v>6.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="H10" t="n">
         <v>10.8</v>
@@ -23369,10 +23369,10 @@
         <v>5.81</v>
       </c>
       <c r="G12" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="H12" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
       <c r="I12" t="n">
         <v>14</v>
@@ -23407,7 +23407,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23439,10 +23439,10 @@
         <v>1.34</v>
       </c>
       <c r="G14" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="H14" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="I14" t="n">
         <v>30</v>
@@ -23477,7 +23477,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I16" t="n">
         <v>19</v>
@@ -23547,7 +23547,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23579,10 +23579,10 @@
         <v>4.76</v>
       </c>
       <c r="G18" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="H18" t="n">
-        <v>9.15</v>
+        <v>9.18</v>
       </c>
       <c r="I18" t="n">
         <v>27</v>
@@ -23614,10 +23614,10 @@
         <v>1.96</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H19" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="I19" t="n">
         <v>22</v>
@@ -23649,10 +23649,10 @@
         <v>4.76</v>
       </c>
       <c r="G20" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="H20" t="n">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
       <c r="I20" t="n">
         <v>27</v>
@@ -23684,10 +23684,10 @@
         <v>0.98</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H21" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
         <v>20</v>
@@ -23719,10 +23719,10 @@
         <v>13.53</v>
       </c>
       <c r="G22" t="n">
-        <v>9.039999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="H22" t="n">
-        <v>19.17</v>
+        <v>19.2</v>
       </c>
       <c r="I22" t="n">
         <v>25</v>
@@ -23754,10 +23754,10 @@
         <v>2.22</v>
       </c>
       <c r="G23" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H23" t="n">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
       <c r="I23" t="n">
         <v>23</v>
@@ -23789,7 +23789,7 @@
         <v>0.59</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H24" t="n">
         <v>2.69</v>
@@ -23827,7 +23827,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="I25" t="n">
         <v>16</v>
@@ -23859,10 +23859,10 @@
         <v>5.84</v>
       </c>
       <c r="G26" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="H26" t="n">
-        <v>10.47</v>
+        <v>10.37</v>
       </c>
       <c r="I26" t="n">
         <v>25</v>
@@ -23897,7 +23897,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="I27" t="n">
         <v>13</v>
@@ -23929,10 +23929,10 @@
         <v>2.6</v>
       </c>
       <c r="G28" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="H28" t="n">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="I28" t="n">
         <v>19</v>
@@ -23967,7 +23967,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="I29" t="n">
         <v>13</v>
@@ -23999,10 +23999,10 @@
         <v>10.07</v>
       </c>
       <c r="G30" t="n">
-        <v>5.91</v>
+        <v>5.89</v>
       </c>
       <c r="H30" t="n">
-        <v>15.96</v>
+        <v>15.81</v>
       </c>
       <c r="I30" t="n">
         <v>51</v>
@@ -24037,7 +24037,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24069,10 +24069,10 @@
         <v>9.35</v>
       </c>
       <c r="G32" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="H32" t="n">
-        <v>15.03</v>
+        <v>15.06</v>
       </c>
       <c r="I32" t="n">
         <v>46</v>
@@ -24107,7 +24107,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -24139,10 +24139,10 @@
         <v>8.26</v>
       </c>
       <c r="G34" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="H34" t="n">
-        <v>14.24</v>
+        <v>14.2</v>
       </c>
       <c r="I34" t="n">
         <v>59</v>
@@ -24177,7 +24177,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -24209,10 +24209,10 @@
         <v>16.53</v>
       </c>
       <c r="G36" t="n">
-        <v>10.71</v>
+        <v>10.83</v>
       </c>
       <c r="H36" t="n">
-        <v>23.97</v>
+        <v>23.9</v>
       </c>
       <c r="I36" t="n">
         <v>70</v>
@@ -24247,7 +24247,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -24279,10 +24279,10 @@
         <v>13.42</v>
       </c>
       <c r="G38" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>19.59</v>
+        <v>19.57</v>
       </c>
       <c r="I38" t="n">
         <v>31</v>
@@ -24314,10 +24314,10 @@
         <v>22.22</v>
       </c>
       <c r="G39" t="n">
-        <v>14.88</v>
+        <v>14.81</v>
       </c>
       <c r="H39" t="n">
-        <v>31.14</v>
+        <v>31.1</v>
       </c>
       <c r="I39" t="n">
         <v>38</v>
@@ -24349,10 +24349,10 @@
         <v>38.93</v>
       </c>
       <c r="G40" t="n">
-        <v>31.37</v>
+        <v>31.38</v>
       </c>
       <c r="H40" t="n">
-        <v>46.87</v>
+        <v>47.06</v>
       </c>
       <c r="I40" t="n">
         <v>79</v>
@@ -24384,10 +24384,10 @@
         <v>30.3</v>
       </c>
       <c r="G41" t="n">
-        <v>22.05</v>
+        <v>22</v>
       </c>
       <c r="H41" t="n">
-        <v>39.81</v>
+        <v>39.75</v>
       </c>
       <c r="I41" t="n">
         <v>49</v>
@@ -24454,10 +24454,10 @@
         <v>0.731</v>
       </c>
       <c r="D2" t="n">
-        <v>0.661</v>
+        <v>0.663</v>
       </c>
       <c r="E2" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -24478,10 +24478,10 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.864</v>
+        <v>0.865</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -24502,7 +24502,7 @@
         <v>0.797</v>
       </c>
       <c r="D4" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="E4" t="n">
         <v>0.846</v>
@@ -24526,7 +24526,7 @@
         <v>0.865</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0.904</v>
@@ -24577,7 +24577,7 @@
         <v>0.76</v>
       </c>
       <c r="E7" t="n">
-        <v>0.872</v>
+        <v>0.871</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -24646,7 +24646,7 @@
         <v>0.761</v>
       </c>
       <c r="D10" t="n">
-        <v>0.694</v>
+        <v>0.696</v>
       </c>
       <c r="E10" t="n">
         <v>0.8120000000000001</v>
@@ -24670,10 +24670,10 @@
         <v>0.802</v>
       </c>
       <c r="D11" t="n">
-        <v>0.735</v>
+        <v>0.734</v>
       </c>
       <c r="E11" t="n">
-        <v>0.854</v>
+        <v>0.853</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -24697,7 +24697,7 @@
         <v>0.767</v>
       </c>
       <c r="E12" t="n">
-        <v>0.875</v>
+        <v>0.876</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -24718,10 +24718,10 @@
         <v>0.847</v>
       </c>
       <c r="D13" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="E13" t="n">
-        <v>0.893</v>
+        <v>0.892</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -24745,7 +24745,7 @@
         <v>0.753</v>
       </c>
       <c r="E14" t="n">
-        <v>0.872</v>
+        <v>0.873</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -24766,10 +24766,10 @@
         <v>0.838</v>
       </c>
       <c r="D15" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="E15" t="n">
-        <v>0.885</v>
+        <v>0.886</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -24790,10 +24790,10 @@
         <v>0.853</v>
       </c>
       <c r="D16" t="n">
-        <v>0.788</v>
+        <v>0.789</v>
       </c>
       <c r="E16" t="n">
-        <v>0.898</v>
+        <v>0.899</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -24817,7 +24817,7 @@
         <v>0.751</v>
       </c>
       <c r="E17" t="n">
-        <v>0.857</v>
+        <v>0.856</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
